--- a/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
@@ -544,19 +544,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -762,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -965,19 +965,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">

--- a/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -88,10 +88,19 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>EVARISTO</t>
-  </si>
-  <si>
-    <t>ALDAIR ALAN</t>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>IRVING URIEL</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
   </si>
 </sst>
 </file>
@@ -713,16 +722,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -736,16 +748,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>96.67</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -759,16 +774,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>96.15000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -782,16 +800,19 @@
         <v>26</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>26</v>
       </c>
-      <c r="E5">
-        <v>26</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -805,16 +826,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -828,16 +852,19 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>94.12</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -851,16 +878,19 @@
         <v>18</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>18</v>
       </c>
-      <c r="E8">
-        <v>18</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -916,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>93.55</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -942,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -977,7 +1007,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1003,7 +1033,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1020,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>94.73999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1046,16 +1076,16 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>97.06</v>
+        <v>94.12</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1081,7 +1111,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1091,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1123,25 +1153,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920097</v>
+        <v>20330051920016</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920425</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,19 +88,10 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>IRVING URIEL</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
   </si>
 </sst>
 </file>
@@ -1050,13 +1041,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
         <v>7.8</v>
@@ -1111,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1159,10 +1150,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1172,29 +1163,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920425</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>IRVING URIEL</t>
   </si>
 </sst>
 </file>
@@ -937,13 +928,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>8.6</v>
@@ -963,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>96.67</v>
+        <v>93.33</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -989,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>96.15000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1024,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1067,16 +1058,16 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>94.12</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1112,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1142,29 +1133,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920016</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20221.xlsx
@@ -613,10 +613,10 @@
         <v>34</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
       <c r="F7">
         <v>33</v>
@@ -625,7 +625,7 @@
         <v>97.06</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -834,10 +834,10 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>32</v>
@@ -1055,10 +1055,10 @@
         <v>34</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>30</v>
@@ -1067,7 +1067,7 @@
         <v>88.23999999999999</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
